--- a/templates/Relatório Conferência.xlsx
+++ b/templates/Relatório Conferência.xlsx
@@ -1,154 +1,47 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rafael\Desktop\WASHCENTER\Planilhas Sistema novo\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3944A98-5C24-464D-AB55-A04CE2B556F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="13176" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="RCOS_29042026" sheetId="1" r:id="rId1"/>
+    <sheet name="RCOS_29042026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">RCOS_29042026!$A$1:$W$1</definedName>
-  </definedNames>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
-  <si>
-    <t>Loja</t>
-  </si>
-  <si>
-    <t>Local</t>
-  </si>
-  <si>
-    <t>Consultor</t>
-  </si>
-  <si>
-    <t>Cor</t>
-  </si>
-  <si>
-    <t>Tonalidade</t>
-  </si>
-  <si>
-    <t>Valor</t>
-  </si>
-  <si>
-    <t>Status Conf.</t>
-  </si>
-  <si>
-    <t>Status Veículo</t>
-  </si>
-  <si>
-    <t>Data da O.S</t>
-  </si>
-  <si>
-    <t>DPTO</t>
-  </si>
-  <si>
-    <t>Placa/ Chassi</t>
-  </si>
-  <si>
-    <t>O.S</t>
-  </si>
-  <si>
-    <t>Cortesia?</t>
-  </si>
-  <si>
-    <t>Retorno?</t>
-  </si>
-  <si>
-    <t>Modelo Veículo</t>
-  </si>
-  <si>
-    <t>Observações</t>
-  </si>
-  <si>
-    <t>NFe</t>
-  </si>
-  <si>
-    <t>Cód Serviço</t>
-  </si>
-  <si>
-    <t>Descrição  Serviço</t>
-  </si>
-  <si>
-    <t>Cód Rolo</t>
-  </si>
-  <si>
-    <t>Instalador</t>
-  </si>
-  <si>
-    <t>✔</t>
-  </si>
-  <si>
-    <t>Obs Conferência</t>
-  </si>
-  <si>
-    <t>Data Cadastro</t>
-  </si>
-  <si>
-    <t>Data Alteração</t>
-  </si>
-  <si>
-    <t>Responsável Cadastro</t>
-  </si>
-  <si>
-    <t>Responsável Alteração</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="3">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
     </font>
     <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FFE8E8E8"/>
       <name val="Google Sans"/>
       <charset val="1"/>
+      <b val="1"/>
+      <color rgb="FFE8E8E8"/>
+      <sz val="12"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -184,18 +77,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="6">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -205,20 +98,17 @@
   <dxfs count="3">
     <dxf>
       <font>
-        <b/>
-        <i val="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <b val="1"/>
         <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
-        <u val="none"/>
+        <condense val="0"/>
+        <color rgb="FFFFFFFF"/>
+        <extend val="0"/>
+        <sz val="11"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
       </font>
       <fill>
         <patternFill patternType="solid">
@@ -226,7 +116,7 @@
           <bgColor theme="4"/>
         </patternFill>
       </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="bottom"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="4" formatCode="#,##0.00"/>
@@ -236,48 +126,109 @@
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{3D173D8E-E7E1-4FB8-BB1C-B4FB1EB1E09D}" name="Tabela2" displayName="Tabela2" ref="A1:AA4" totalsRowShown="0" headerRowDxfId="0">
-  <autoFilter ref="A1:AA4" xr:uid="{3D173D8E-E7E1-4FB8-BB1C-B4FB1EB1E09D}"/>
-  <tableColumns count="27">
-    <tableColumn id="1" xr3:uid="{F6D73193-4EBA-4B33-BB11-F976E6A45EE4}" name="Data da O.S"/>
-    <tableColumn id="2" xr3:uid="{C3F0860E-C765-46DF-80E6-1FA6B40B6A5E}" name="Loja"/>
-    <tableColumn id="3" xr3:uid="{94678372-30E1-40A6-9B94-67B58BC1501F}" name="Local"/>
-    <tableColumn id="4" xr3:uid="{0CA40B87-DFBF-45CF-A9E0-420D75008234}" name="DPTO"/>
-    <tableColumn id="5" xr3:uid="{7E77BDF5-244E-4941-918B-A8ABFD47DAD2}" name="Placa/ Chassi"/>
-    <tableColumn id="6" xr3:uid="{6C1F7183-156A-4B2B-B7D1-CA6D8FF352FF}" name="O.S"/>
-    <tableColumn id="7" xr3:uid="{F00E79C3-8831-4DD0-AB4E-52CD82A0489E}" name="Cortesia?"/>
-    <tableColumn id="8" xr3:uid="{67E9C3F8-8CE1-4642-98AE-4B1A08FFBDFA}" name="Retorno?"/>
-    <tableColumn id="9" xr3:uid="{93D0B3CD-7849-4E15-B8D1-DA8615E185F6}" name="Consultor"/>
-    <tableColumn id="10" xr3:uid="{0FDD0533-E998-46EF-989A-0A5C50DA9238}" name="Modelo Veículo"/>
-    <tableColumn id="11" xr3:uid="{F993EB8D-6B4A-45A6-8E0E-A0363D1359B7}" name="Cor"/>
-    <tableColumn id="12" xr3:uid="{AB4E5FC6-BC64-4367-9F1A-A4E9497D80DC}" name="Observações"/>
-    <tableColumn id="13" xr3:uid="{BFEFA117-DB80-420A-8CD1-EC14819B7AA1}" name="NFe"/>
-    <tableColumn id="14" xr3:uid="{7042B082-8314-49D0-80AA-BB1FAD8ED30C}" name="Cód Serviço"/>
-    <tableColumn id="15" xr3:uid="{1E4D5E21-C3F9-414C-BD50-FDB78E01C6E4}" name="Descrição  Serviço"/>
-    <tableColumn id="16" xr3:uid="{C17524A9-24FE-4F32-B502-C031310277B8}" name="Tonalidade"/>
-    <tableColumn id="17" xr3:uid="{5E4F83D6-F314-486B-AE67-4EF7A6E075C8}" name="Cód Rolo" dataDxfId="2"/>
-    <tableColumn id="18" xr3:uid="{902213A0-7AE8-426B-8F14-BCA5ADEC3DE1}" name="Instalador"/>
-    <tableColumn id="19" xr3:uid="{6C8AABC1-991D-4E5F-A53C-2CA0066A0310}" name="Valor"/>
-    <tableColumn id="20" xr3:uid="{6DCE7FBA-AAD5-4274-A028-981DACC0DDF9}" name="✔"/>
-    <tableColumn id="21" xr3:uid="{188B618D-0046-4E36-951C-4AF9A0D93A2C}" name="Obs Conferência" dataDxfId="1"/>
-    <tableColumn id="22" xr3:uid="{CA5B1842-74F0-4539-ACB0-7AD34FD27244}" name="Status Conf."/>
-    <tableColumn id="23" xr3:uid="{E5C6631C-012D-4B59-AD84-149AFB0CDF0E}" name="Status Veículo"/>
-    <tableColumn id="24" xr3:uid="{81692872-D906-48B6-8345-F39865B10D15}" name="Data Cadastro"/>
-    <tableColumn id="25" xr3:uid="{72657BDD-6301-48E2-B707-B4E5639849D7}" name="Responsável Cadastro"/>
-    <tableColumn id="26" xr3:uid="{67D3C48E-5B07-472B-92ED-DADB8BE1D530}" name="Data Alteração"/>
-    <tableColumn id="27" xr3:uid="{52281E25-50E9-466C-86BE-A2F4AB15E099}" name="Responsável Alteração"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabela2" displayName="Tabela2" ref="A1:AB4" headerRowCount="1" totalsRowShown="0" headerRowDxfId="0">
+  <autoFilter ref="A1:AB4"/>
+  <tableColumns count="28">
+    <tableColumn id="1" name="Data da O.S"/>
+    <tableColumn id="2" name="Loja"/>
+    <tableColumn id="3" name="Local"/>
+    <tableColumn id="4" name="DPTO"/>
+    <tableColumn id="5" name="Placa/ Chassi"/>
+    <tableColumn id="6" name="O.S"/>
+    <tableColumn id="7" name="Cortesia?"/>
+    <tableColumn id="8" name="Retorno?"/>
+    <tableColumn id="9" name="Consultor"/>
+    <tableColumn id="10" name="Modelo Veículo"/>
+    <tableColumn id="11" name="Cor"/>
+    <tableColumn id="12" name="Briefing do Consultor"/>
+    <tableColumn id="13" name="Relato Técnico do Instalador"/>
+    <tableColumn id="14" name="NFe"/>
+    <tableColumn id="15" name="Cód Serviço"/>
+    <tableColumn id="16" name="Descrição  Serviço"/>
+    <tableColumn id="17" name="Tonalidade"/>
+    <tableColumn id="18" name="Cód Rolo" dataDxfId="2"/>
+    <tableColumn id="19" name="Instalador"/>
+    <tableColumn id="20" name="Valor"/>
+    <tableColumn id="21" name="✔"/>
+    <tableColumn id="22" name="Obs Conferência" dataDxfId="1"/>
+    <tableColumn id="23" name="Status Conf."/>
+    <tableColumn id="24" name="Status Veículo"/>
+    <tableColumn id="25" name="Data Cadastro"/>
+    <tableColumn id="26" name="Responsável Cadastro"/>
+    <tableColumn id="27" name="Data Alteração"/>
+    <tableColumn id="28" name="Responsável Alteração"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -599,163 +550,226 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AA10"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AB10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="19.85546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.5703125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.85546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="21.42578125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="20.28515625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="15.140625" customWidth="1"/>
-    <col min="25" max="25" width="22" customWidth="1"/>
-    <col min="26" max="26" width="15.7109375" customWidth="1"/>
-    <col min="27" max="27" width="22.5703125" customWidth="1"/>
-    <col min="28" max="28" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col width="15.7109375" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="9.28515625" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="10.140625" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="10.42578125" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="17" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="8.5703125" bestFit="1" customWidth="1" min="6" max="6"/>
+    <col width="13.85546875" bestFit="1" customWidth="1" min="7" max="7"/>
+    <col width="13.7109375" bestFit="1" customWidth="1" min="8" max="8"/>
+    <col width="14.140625" bestFit="1" customWidth="1" min="9" max="9"/>
+    <col width="19.85546875" bestFit="1" customWidth="1" min="10" max="10"/>
+    <col width="8.5703125" bestFit="1" customWidth="1" min="11" max="11"/>
+    <col width="23" bestFit="1" customWidth="1" min="12" max="12"/>
+    <col width="28" bestFit="1" customWidth="1" min="13" max="13"/>
+    <col width="9.140625" bestFit="1" customWidth="1" min="14" max="14"/>
+    <col width="15.85546875" bestFit="1" customWidth="1" min="15" max="15"/>
+    <col width="21.42578125" bestFit="1" customWidth="1" min="16" max="16"/>
+    <col width="15.42578125" bestFit="1" customWidth="1" min="17" max="17"/>
+    <col width="13.42578125" bestFit="1" customWidth="1" min="18" max="18"/>
+    <col width="14.42578125" bestFit="1" customWidth="1" min="19" max="19"/>
+    <col width="10.28515625" bestFit="1" customWidth="1" min="20" max="20"/>
+    <col width="7.85546875" bestFit="1" customWidth="1" min="21" max="21"/>
+    <col width="20.28515625" bestFit="1" customWidth="1" min="22" max="22"/>
+    <col width="16.140625" bestFit="1" customWidth="1" min="23" max="23"/>
+    <col width="18.28515625" customWidth="1" min="24" max="24"/>
+    <col width="15.140625" customWidth="1" min="25" max="25"/>
+    <col width="22" customWidth="1" min="26" max="26"/>
+    <col width="15.7109375" customWidth="1" min="27" max="27"/>
+    <col width="22.5703125" bestFit="1" customWidth="1" min="28" max="28"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="15" customHeight="1" thickBot="1">
-      <c r="A1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="N1" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="O1" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="P1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q1" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="R1" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="S1" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T1" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="U1" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="V1" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="W1" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="X1" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="Y1" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="Z1" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="AA1" s="5" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="2" spans="1:27">
-      <c r="Q2" s="1"/>
-      <c r="U2" s="1"/>
-    </row>
-    <row r="3" spans="1:27">
-      <c r="Q3" s="1"/>
-      <c r="U3" s="1"/>
-    </row>
-    <row r="4" spans="1:27">
-      <c r="Q4" s="1"/>
-      <c r="U4" s="1"/>
-    </row>
-    <row r="5" spans="1:27">
-      <c r="Q5" s="1"/>
-      <c r="U5" s="1"/>
-    </row>
-    <row r="6" spans="1:27">
-      <c r="Q6" s="1"/>
-      <c r="U6" s="1"/>
-    </row>
-    <row r="7" spans="1:27">
-      <c r="Q7" s="1"/>
-      <c r="U7" s="1"/>
-    </row>
-    <row r="8" spans="1:27">
-      <c r="Q8" s="1"/>
-      <c r="U8" s="1"/>
-    </row>
-    <row r="9" spans="1:27">
-      <c r="Q9" s="1"/>
-      <c r="U9" s="1"/>
-    </row>
-    <row r="10" spans="1:27">
-      <c r="Q10" s="1"/>
-      <c r="U10" s="1"/>
+    <row r="1" ht="15" customHeight="1" thickBot="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Data da O.S</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Loja</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>DPTO</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Placa/ Chassi</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>O.S</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Cortesia?</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Retorno?</t>
+        </is>
+      </c>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Consultor</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="inlineStr">
+        <is>
+          <t>Modelo Veículo</t>
+        </is>
+      </c>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Cor</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="inlineStr">
+        <is>
+          <t>Briefing do Consultor</t>
+        </is>
+      </c>
+      <c r="M1" s="3" t="inlineStr">
+        <is>
+          <t>Relato Técnico do Instalador</t>
+        </is>
+      </c>
+      <c r="N1" s="3" t="inlineStr">
+        <is>
+          <t>NFe</t>
+        </is>
+      </c>
+      <c r="O1" s="3" t="inlineStr">
+        <is>
+          <t>Cód Serviço</t>
+        </is>
+      </c>
+      <c r="P1" s="3" t="inlineStr">
+        <is>
+          <t>Descrição  Serviço</t>
+        </is>
+      </c>
+      <c r="Q1" s="3" t="inlineStr">
+        <is>
+          <t>Tonalidade</t>
+        </is>
+      </c>
+      <c r="R1" s="3" t="inlineStr">
+        <is>
+          <t>Cód Rolo</t>
+        </is>
+      </c>
+      <c r="S1" s="3" t="inlineStr">
+        <is>
+          <t>Instalador</t>
+        </is>
+      </c>
+      <c r="T1" s="3" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+      <c r="U1" s="4" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="V1" s="3" t="inlineStr">
+        <is>
+          <t>Obs Conferência</t>
+        </is>
+      </c>
+      <c r="W1" s="3" t="inlineStr">
+        <is>
+          <t>Status Conf.</t>
+        </is>
+      </c>
+      <c r="X1" s="3" t="inlineStr">
+        <is>
+          <t>Status Veículo</t>
+        </is>
+      </c>
+      <c r="Y1" s="3" t="inlineStr">
+        <is>
+          <t>Data Cadastro</t>
+        </is>
+      </c>
+      <c r="Z1" s="3" t="inlineStr">
+        <is>
+          <t>Responsável Cadastro</t>
+        </is>
+      </c>
+      <c r="AA1" s="3" t="inlineStr">
+        <is>
+          <t>Data Alteração</t>
+        </is>
+      </c>
+      <c r="AB1" s="5" t="inlineStr">
+        <is>
+          <t>Responsável Alteração</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="R2" s="1" t="n"/>
+      <c r="V2" s="1" t="n"/>
+    </row>
+    <row r="3">
+      <c r="R3" s="1" t="n"/>
+      <c r="V3" s="1" t="n"/>
+    </row>
+    <row r="4">
+      <c r="R4" s="1" t="n"/>
+      <c r="V4" s="1" t="n"/>
+    </row>
+    <row r="5">
+      <c r="R5" s="1" t="n"/>
+      <c r="V5" s="1" t="n"/>
+    </row>
+    <row r="6">
+      <c r="R6" s="1" t="n"/>
+      <c r="V6" s="1" t="n"/>
+    </row>
+    <row r="7">
+      <c r="R7" s="1" t="n"/>
+      <c r="V7" s="1" t="n"/>
+    </row>
+    <row r="8">
+      <c r="R8" s="1" t="n"/>
+      <c r="V8" s="1" t="n"/>
+    </row>
+    <row r="9">
+      <c r="R9" s="1" t="n"/>
+      <c r="V9" s="1" t="n"/>
+    </row>
+    <row r="10">
+      <c r="R10" s="1" t="n"/>
+      <c r="V10" s="1" t="n"/>
     </row>
   </sheetData>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.787401575" bottom="0.787401575" header="0.31496062" footer="0.31496062"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>